--- a/harbiy_muassasalar.xlsx
+++ b/harbiy_muassasalar.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$AG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$AF$1</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>inst_type</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>review_video_url</t>
-  </si>
-  <si>
-    <t>overview_text</t>
   </si>
   <si>
     <t>eligibility_criteria</t>
@@ -116,10 +113,6 @@
   <si>
     <t>Kimlar qabul qilinadi:
 - 9-sinfni bitirgan o'quvchilar (o'g'il va qiz bolalar);</t>
-  </si>
-  <si>
-    <t>O'qish davomida:
-- Bepul yotoqxona;</t>
   </si>
   <si>
     <t>admission_date</t>
@@ -139,9 +132,6 @@
     <t>Tarix</t>
   </si>
   <si>
-    <t>Ingliz tili</t>
-  </si>
-  <si>
     <t>Ona tili</t>
   </si>
   <si>
@@ -161,16 +151,85 @@
   </si>
   <si>
     <t>subject_third</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/2</t>
+  </si>
+  <si>
+    <t>Barcha viloyatlar</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/3
+https://t.me/Mini_app_bazaaaaa/4
+https://t.me/Mini_app_bazaaaaa/5
+https://t.me/Mini_app_bazaaaaa/6</t>
+  </si>
+  <si>
+    <t>Imtiyozli abituriyentlar:
+- Oxirgi 2 yilda Sport turnirlari va fan
+olimpiadasi respublika bosqichi g’oliblari;
+- Xizmat chog’ida vafot qilgan yoki
+nogiron bo’lib qolgan harbiy xodimlar
+farzandlari;
+- Ichki ishlar vaziri tavsiyasi bilan organ
+xodimi farzandlari (5% li kvota asosida);
+O'qish davomida:
+- Bepul yotoqxona;
+Bitiruvchilar:
+- Ichki ishlar akademiyasining
+90% talabasi shu litseydan
+tanlab suhbat asosida olinadi;
+-  10 foizlik ball – (19 ball)
+FVV va Milliy gvardiya
+institutiga kirish uchun beriladi;</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/7</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/8</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/9</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/10</t>
+  </si>
+  <si>
+    <t>Axborot xavfsizligi (o'zbek)</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/12</t>
+  </si>
+  <si>
+    <t>Matematika</t>
+  </si>
+  <si>
+    <t>Informatika</t>
+  </si>
+  <si>
+    <t>Chet tili</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -208,10 +267,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -225,8 +285,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -526,45 +590,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG78"/>
+  <dimension ref="A1:AF78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" style="1" customWidth="1"/>
     <col min="5" max="6" width="9.140625" style="1"/>
     <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.140625" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.140625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -575,7 +638,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -598,59 +661,59 @@
       <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AB1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>25</v>
@@ -661,113 +724,176 @@
       <c r="AF1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:32" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="L2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="3" t="s">
-        <v>44</v>
+      <c r="Y2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>86</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+    </row>
+    <row r="3" spans="1:32" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="3"/>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
+      <c r="Y3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>56</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="AE3" s="2"/>
       <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -779,30 +905,29 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -814,30 +939,29 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -849,30 +973,29 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -884,30 +1007,29 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -919,30 +1041,29 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
-      <c r="AG8" s="2"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -954,30 +1075,29 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
       <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -989,30 +1109,29 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1024,30 +1143,29 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
       <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1059,30 +1177,29 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
       <c r="AF12" s="2"/>
-      <c r="AG12" s="2"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1094,30 +1211,29 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
       <c r="AE13" s="2"/>
       <c r="AF13" s="2"/>
-      <c r="AG13" s="2"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1129,30 +1245,29 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
       <c r="AE14" s="2"/>
       <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1164,30 +1279,29 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
       <c r="AE15" s="2"/>
       <c r="AF15" s="2"/>
-      <c r="AG15" s="2"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1199,30 +1313,29 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="2"/>
       <c r="AE16" s="2"/>
       <c r="AF16" s="2"/>
-      <c r="AG16" s="2"/>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1234,30 +1347,29 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="2"/>
       <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1269,30 +1381,29 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="2"/>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
-      <c r="AG18" s="2"/>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1304,30 +1415,29 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="2"/>
       <c r="AE19" s="2"/>
       <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1339,30 +1449,29 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
-      <c r="AG20" s="2"/>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1374,30 +1483,29 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="2"/>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
       <c r="AE21" s="2"/>
       <c r="AF21" s="2"/>
-      <c r="AG21" s="2"/>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1409,30 +1517,29 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="2"/>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="2"/>
       <c r="AE22" s="2"/>
       <c r="AF22" s="2"/>
-      <c r="AG22" s="2"/>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1444,30 +1551,29 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="2"/>
       <c r="AE23" s="2"/>
       <c r="AF23" s="2"/>
-      <c r="AG23" s="2"/>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1479,30 +1585,29 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="2"/>
       <c r="AE24" s="2"/>
       <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1514,30 +1619,29 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="2"/>
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="2"/>
       <c r="AE25" s="2"/>
       <c r="AF25" s="2"/>
-      <c r="AG25" s="2"/>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1549,30 +1653,29 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="2"/>
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="2"/>
       <c r="AE26" s="2"/>
       <c r="AF26" s="2"/>
-      <c r="AG26" s="2"/>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1584,30 +1687,29 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="2"/>
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="2"/>
       <c r="AE27" s="2"/>
       <c r="AF27" s="2"/>
-      <c r="AG27" s="2"/>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1619,30 +1721,29 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="2"/>
       <c r="AE28" s="2"/>
       <c r="AF28" s="2"/>
-      <c r="AG28" s="2"/>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1654,30 +1755,29 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="2"/>
       <c r="AE29" s="2"/>
       <c r="AF29" s="2"/>
-      <c r="AG29" s="2"/>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1689,30 +1789,29 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="2"/>
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
-      <c r="AG30" s="2"/>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -1724,30 +1823,29 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
-      <c r="Z31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="2"/>
       <c r="AE31" s="2"/>
       <c r="AF31" s="2"/>
-      <c r="AG31" s="2"/>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1759,30 +1857,29 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="2"/>
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
-      <c r="AG32" s="2"/>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1794,30 +1891,29 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
       <c r="AE33" s="2"/>
       <c r="AF33" s="2"/>
-      <c r="AG33" s="2"/>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1829,30 +1925,29 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
-      <c r="Y34" s="2"/>
-      <c r="Z34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="2"/>
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
-      <c r="AG34" s="2"/>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1864,30 +1959,29 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
-      <c r="Y35" s="2"/>
-      <c r="Z35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="2"/>
       <c r="AE35" s="2"/>
       <c r="AF35" s="2"/>
-      <c r="AG35" s="2"/>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1899,30 +1993,29 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
-      <c r="Y36" s="2"/>
-      <c r="Z36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
       <c r="AB36" s="2"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="2"/>
       <c r="AE36" s="2"/>
       <c r="AF36" s="2"/>
-      <c r="AG36" s="2"/>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1934,30 +2027,29 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="2"/>
-      <c r="U37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
-      <c r="Y37" s="2"/>
-      <c r="Z37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
-      <c r="AG37" s="2"/>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1969,30 +2061,29 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="2"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="2"/>
       <c r="AE38" s="2"/>
       <c r="AF38" s="2"/>
-      <c r="AG38" s="2"/>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2004,30 +2095,29 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="2"/>
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
-      <c r="Y39" s="2"/>
-      <c r="Z39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
       <c r="AB39" s="2"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="2"/>
       <c r="AE39" s="2"/>
       <c r="AF39" s="2"/>
-      <c r="AG39" s="2"/>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2039,30 +2129,29 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="2"/>
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
-      <c r="Y40" s="2"/>
-      <c r="Z40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
       <c r="AB40" s="2"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="2"/>
       <c r="AE40" s="2"/>
       <c r="AF40" s="2"/>
-      <c r="AG40" s="2"/>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2074,30 +2163,29 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="2"/>
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
-      <c r="Z41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
       <c r="AB41" s="2"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="2"/>
       <c r="AE41" s="2"/>
       <c r="AF41" s="2"/>
-      <c r="AG41" s="2"/>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2109,30 +2197,29 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="2"/>
-      <c r="U42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="2"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
-      <c r="Y42" s="2"/>
-      <c r="Z42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
       <c r="AB42" s="2"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="2"/>
       <c r="AE42" s="2"/>
       <c r="AF42" s="2"/>
-      <c r="AG42" s="2"/>
-    </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2144,30 +2231,29 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="2"/>
-      <c r="U43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="2"/>
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
-      <c r="Y43" s="2"/>
-      <c r="Z43" s="3"/>
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="2"/>
       <c r="AE43" s="2"/>
       <c r="AF43" s="2"/>
-      <c r="AG43" s="2"/>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2179,30 +2265,29 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="2"/>
-      <c r="U44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
-      <c r="Y44" s="2"/>
-      <c r="Z44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
       <c r="AB44" s="2"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="2"/>
       <c r="AE44" s="2"/>
       <c r="AF44" s="2"/>
-      <c r="AG44" s="2"/>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2214,30 +2299,29 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="2"/>
-      <c r="U45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="2"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="2"/>
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
-      <c r="Y45" s="2"/>
-      <c r="Z45" s="3"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
       <c r="AB45" s="2"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="2"/>
       <c r="AE45" s="2"/>
       <c r="AF45" s="2"/>
-      <c r="AG45" s="2"/>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2249,30 +2333,29 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="2"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="2"/>
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="2"/>
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
-      <c r="AG46" s="2"/>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2284,30 +2367,29 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="2"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="3"/>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
       <c r="AB47" s="2"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="2"/>
       <c r="AE47" s="2"/>
       <c r="AF47" s="2"/>
-      <c r="AG47" s="2"/>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2319,30 +2401,29 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="2"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
-      <c r="Y48" s="2"/>
-      <c r="Z48" s="3"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
       <c r="AB48" s="2"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="2"/>
       <c r="AE48" s="2"/>
       <c r="AF48" s="2"/>
-      <c r="AG48" s="2"/>
-    </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2354,30 +2435,29 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="2"/>
-      <c r="U49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="2"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="3"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
       <c r="AB49" s="2"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="2"/>
       <c r="AE49" s="2"/>
       <c r="AF49" s="2"/>
-      <c r="AG49" s="2"/>
-    </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2389,30 +2469,29 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="2"/>
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
       <c r="AB50" s="2"/>
       <c r="AC50" s="2"/>
       <c r="AD50" s="2"/>
       <c r="AE50" s="2"/>
       <c r="AF50" s="2"/>
-      <c r="AG50" s="2"/>
-    </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2424,30 +2503,29 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="2"/>
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="3"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
       <c r="AB51" s="2"/>
       <c r="AC51" s="2"/>
       <c r="AD51" s="2"/>
       <c r="AE51" s="2"/>
       <c r="AF51" s="2"/>
-      <c r="AG51" s="2"/>
-    </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2459,30 +2537,29 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="2"/>
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
-      <c r="Y52" s="2"/>
-      <c r="Z52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
       <c r="AB52" s="2"/>
       <c r="AC52" s="2"/>
       <c r="AD52" s="2"/>
       <c r="AE52" s="2"/>
       <c r="AF52" s="2"/>
-      <c r="AG52" s="2"/>
-    </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2494,30 +2571,29 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="2"/>
       <c r="V53" s="2"/>
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-      <c r="Z53" s="3"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
       <c r="AB53" s="2"/>
       <c r="AC53" s="2"/>
       <c r="AD53" s="2"/>
       <c r="AE53" s="2"/>
       <c r="AF53" s="2"/>
-      <c r="AG53" s="2"/>
-    </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2529,30 +2605,29 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="2"/>
-      <c r="U54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="2"/>
       <c r="V54" s="2"/>
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
-      <c r="Y54" s="2"/>
-      <c r="Z54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="2"/>
       <c r="AA54" s="2"/>
       <c r="AB54" s="2"/>
       <c r="AC54" s="2"/>
       <c r="AD54" s="2"/>
       <c r="AE54" s="2"/>
       <c r="AF54" s="2"/>
-      <c r="AG54" s="2"/>
-    </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2564,30 +2639,29 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="2"/>
-      <c r="U55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="2"/>
       <c r="V55" s="2"/>
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
-      <c r="Y55" s="2"/>
-      <c r="Z55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
       <c r="AB55" s="2"/>
       <c r="AC55" s="2"/>
       <c r="AD55" s="2"/>
       <c r="AE55" s="2"/>
       <c r="AF55" s="2"/>
-      <c r="AG55" s="2"/>
-    </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2599,30 +2673,29 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="2"/>
-      <c r="U56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="2"/>
       <c r="V56" s="2"/>
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
-      <c r="Y56" s="2"/>
-      <c r="Z56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
       <c r="AB56" s="2"/>
       <c r="AC56" s="2"/>
       <c r="AD56" s="2"/>
       <c r="AE56" s="2"/>
       <c r="AF56" s="2"/>
-      <c r="AG56" s="2"/>
-    </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2634,30 +2707,29 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="2"/>
-      <c r="U57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="2"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="2"/>
       <c r="V57" s="2"/>
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
-      <c r="Y57" s="2"/>
-      <c r="Z57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
       <c r="AB57" s="2"/>
       <c r="AC57" s="2"/>
       <c r="AD57" s="2"/>
       <c r="AE57" s="2"/>
       <c r="AF57" s="2"/>
-      <c r="AG57" s="2"/>
-    </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2669,30 +2741,29 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="3"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="2"/>
-      <c r="U58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="2"/>
       <c r="V58" s="2"/>
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
-      <c r="Z58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
       <c r="AB58" s="2"/>
       <c r="AC58" s="2"/>
       <c r="AD58" s="2"/>
       <c r="AE58" s="2"/>
       <c r="AF58" s="2"/>
-      <c r="AG58" s="2"/>
-    </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2704,30 +2775,29 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="2"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="2"/>
       <c r="V59" s="2"/>
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
       <c r="AB59" s="2"/>
       <c r="AC59" s="2"/>
       <c r="AD59" s="2"/>
       <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
-      <c r="AG59" s="2"/>
-    </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2739,30 +2809,29 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="2"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
-      <c r="Y60" s="2"/>
-      <c r="Z60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
       <c r="AB60" s="2"/>
       <c r="AC60" s="2"/>
       <c r="AD60" s="2"/>
       <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
-      <c r="AG60" s="2"/>
-    </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2774,30 +2843,29 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="2"/>
-      <c r="U61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="2"/>
       <c r="V61" s="2"/>
       <c r="W61" s="2"/>
       <c r="X61" s="2"/>
-      <c r="Y61" s="2"/>
-      <c r="Z61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
       <c r="AB61" s="2"/>
       <c r="AC61" s="2"/>
       <c r="AD61" s="2"/>
       <c r="AE61" s="2"/>
       <c r="AF61" s="2"/>
-      <c r="AG61" s="2"/>
-    </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2809,30 +2877,29 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="2"/>
-      <c r="Q62" s="3"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="2"/>
-      <c r="U62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="2"/>
       <c r="V62" s="2"/>
       <c r="W62" s="2"/>
       <c r="X62" s="2"/>
-      <c r="Y62" s="2"/>
-      <c r="Z62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
       <c r="AB62" s="2"/>
       <c r="AC62" s="2"/>
       <c r="AD62" s="2"/>
       <c r="AE62" s="2"/>
       <c r="AF62" s="2"/>
-      <c r="AG62" s="2"/>
-    </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2844,30 +2911,29 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="2"/>
-      <c r="U63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="2"/>
       <c r="V63" s="2"/>
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
-      <c r="Y63" s="2"/>
-      <c r="Z63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
       <c r="AB63" s="2"/>
       <c r="AC63" s="2"/>
       <c r="AD63" s="2"/>
       <c r="AE63" s="2"/>
       <c r="AF63" s="2"/>
-      <c r="AG63" s="2"/>
-    </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2879,30 +2945,29 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="2"/>
-      <c r="U64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="2"/>
       <c r="V64" s="2"/>
       <c r="W64" s="2"/>
       <c r="X64" s="2"/>
-      <c r="Y64" s="2"/>
-      <c r="Z64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="2"/>
       <c r="AA64" s="2"/>
       <c r="AB64" s="2"/>
       <c r="AC64" s="2"/>
       <c r="AD64" s="2"/>
       <c r="AE64" s="2"/>
       <c r="AF64" s="2"/>
-      <c r="AG64" s="2"/>
-    </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2914,30 +2979,29 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="2"/>
-      <c r="U65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="2"/>
       <c r="V65" s="2"/>
       <c r="W65" s="2"/>
       <c r="X65" s="2"/>
-      <c r="Y65" s="2"/>
-      <c r="Z65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
       <c r="AB65" s="2"/>
       <c r="AC65" s="2"/>
       <c r="AD65" s="2"/>
       <c r="AE65" s="2"/>
       <c r="AF65" s="2"/>
-      <c r="AG65" s="2"/>
-    </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2949,30 +3013,29 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="3"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="2"/>
       <c r="V66" s="2"/>
       <c r="W66" s="2"/>
       <c r="X66" s="2"/>
-      <c r="Y66" s="2"/>
-      <c r="Z66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
       <c r="AB66" s="2"/>
       <c r="AC66" s="2"/>
       <c r="AD66" s="2"/>
       <c r="AE66" s="2"/>
       <c r="AF66" s="2"/>
-      <c r="AG66" s="2"/>
-    </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2984,30 +3047,29 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="2"/>
       <c r="V67" s="2"/>
       <c r="W67" s="2"/>
       <c r="X67" s="2"/>
-      <c r="Y67" s="2"/>
-      <c r="Z67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
       <c r="AB67" s="2"/>
       <c r="AC67" s="2"/>
       <c r="AD67" s="2"/>
       <c r="AE67" s="2"/>
       <c r="AF67" s="2"/>
-      <c r="AG67" s="2"/>
-    </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3019,30 +3081,29 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="3"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="2"/>
       <c r="V68" s="2"/>
       <c r="W68" s="2"/>
       <c r="X68" s="2"/>
-      <c r="Y68" s="2"/>
-      <c r="Z68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
       <c r="AB68" s="2"/>
       <c r="AC68" s="2"/>
       <c r="AD68" s="2"/>
       <c r="AE68" s="2"/>
       <c r="AF68" s="2"/>
-      <c r="AG68" s="2"/>
-    </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3054,30 +3115,29 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="2"/>
-      <c r="U69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="2"/>
       <c r="V69" s="2"/>
       <c r="W69" s="2"/>
       <c r="X69" s="2"/>
-      <c r="Y69" s="2"/>
-      <c r="Z69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
       <c r="AB69" s="2"/>
       <c r="AC69" s="2"/>
       <c r="AD69" s="2"/>
       <c r="AE69" s="2"/>
       <c r="AF69" s="2"/>
-      <c r="AG69" s="2"/>
-    </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3089,30 +3149,29 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="2"/>
-      <c r="U70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="2"/>
       <c r="V70" s="2"/>
       <c r="W70" s="2"/>
       <c r="X70" s="2"/>
-      <c r="Y70" s="2"/>
-      <c r="Z70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
       <c r="AB70" s="2"/>
       <c r="AC70" s="2"/>
       <c r="AD70" s="2"/>
       <c r="AE70" s="2"/>
       <c r="AF70" s="2"/>
-      <c r="AG70" s="2"/>
-    </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3124,30 +3183,29 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="3"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="2"/>
       <c r="V71" s="2"/>
       <c r="W71" s="2"/>
       <c r="X71" s="2"/>
-      <c r="Y71" s="2"/>
-      <c r="Z71" s="3"/>
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
       <c r="AB71" s="2"/>
       <c r="AC71" s="2"/>
       <c r="AD71" s="2"/>
       <c r="AE71" s="2"/>
       <c r="AF71" s="2"/>
-      <c r="AG71" s="2"/>
-    </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3159,30 +3217,29 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="3"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="2"/>
       <c r="V72" s="2"/>
       <c r="W72" s="2"/>
       <c r="X72" s="2"/>
-      <c r="Y72" s="2"/>
-      <c r="Z72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
       <c r="AB72" s="2"/>
       <c r="AC72" s="2"/>
       <c r="AD72" s="2"/>
       <c r="AE72" s="2"/>
       <c r="AF72" s="2"/>
-      <c r="AG72" s="2"/>
-    </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3194,30 +3251,29 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="2"/>
-      <c r="U73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="2"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="2"/>
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
       <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
-      <c r="Z73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
       <c r="AB73" s="2"/>
       <c r="AC73" s="2"/>
       <c r="AD73" s="2"/>
       <c r="AE73" s="2"/>
       <c r="AF73" s="2"/>
-      <c r="AG73" s="2"/>
-    </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3229,30 +3285,29 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="2"/>
-      <c r="U74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="2"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="2"/>
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
       <c r="X74" s="2"/>
-      <c r="Y74" s="2"/>
-      <c r="Z74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
       <c r="AB74" s="2"/>
       <c r="AC74" s="2"/>
       <c r="AD74" s="2"/>
       <c r="AE74" s="2"/>
       <c r="AF74" s="2"/>
-      <c r="AG74" s="2"/>
-    </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3264,30 +3319,29 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="2"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="2"/>
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
       <c r="X75" s="2"/>
-      <c r="Y75" s="2"/>
-      <c r="Z75" s="3"/>
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
       <c r="AB75" s="2"/>
       <c r="AC75" s="2"/>
       <c r="AD75" s="2"/>
       <c r="AE75" s="2"/>
       <c r="AF75" s="2"/>
-      <c r="AG75" s="2"/>
-    </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3299,30 +3353,29 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="3"/>
-      <c r="T76" s="2"/>
-      <c r="U76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="2"/>
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
       <c r="X76" s="2"/>
-      <c r="Y76" s="2"/>
-      <c r="Z76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
       <c r="AB76" s="2"/>
       <c r="AC76" s="2"/>
       <c r="AD76" s="2"/>
       <c r="AE76" s="2"/>
       <c r="AF76" s="2"/>
-      <c r="AG76" s="2"/>
-    </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3334,30 +3387,29 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="2"/>
-      <c r="U77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="2"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="2"/>
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
       <c r="X77" s="2"/>
-      <c r="Y77" s="2"/>
-      <c r="Z77" s="3"/>
+      <c r="Y77" s="3"/>
+      <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
       <c r="AB77" s="2"/>
       <c r="AC77" s="2"/>
       <c r="AD77" s="2"/>
       <c r="AE77" s="2"/>
       <c r="AF77" s="2"/>
-      <c r="AG77" s="2"/>
-    </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3369,33 +3421,46 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="3"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="3"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="2"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="2"/>
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
       <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-      <c r="Z78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="2"/>
       <c r="AA78" s="2"/>
       <c r="AB78" s="2"/>
       <c r="AC78" s="2"/>
       <c r="AD78" s="2"/>
       <c r="AE78" s="2"/>
       <c r="AF78" s="2"/>
-      <c r="AG78" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1"/>
+  <autoFilter ref="A1:AF1"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="M2" r:id="rId2"/>
+    <hyperlink ref="O2" r:id="rId3"/>
+    <hyperlink ref="Q2" r:id="rId4"/>
+    <hyperlink ref="S2" r:id="rId5"/>
+    <hyperlink ref="AD2" r:id="rId6"/>
+    <hyperlink ref="E3" r:id="rId7"/>
+    <hyperlink ref="M3" r:id="rId8"/>
+    <hyperlink ref="O3" r:id="rId9"/>
+    <hyperlink ref="Q3" r:id="rId10"/>
+    <hyperlink ref="S3" r:id="rId11"/>
+    <hyperlink ref="AD3" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
 

--- a/harbiy_muassasalar.xlsx
+++ b/harbiy_muassasalar.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="121">
   <si>
     <t>inst_type</t>
   </si>
@@ -109,10 +109,6 @@
   </si>
   <si>
     <t>IIV HAL</t>
-  </si>
-  <si>
-    <t>Kimlar qabul qilinadi:
-- 9-sinfni bitirgan o'quvchilar (o'g'il va qiz bolalar);</t>
   </si>
   <si>
     <t>admission_date</t>
@@ -157,12 +153,6 @@
   </si>
   <si>
     <t>Barcha viloyatlar</t>
-  </si>
-  <si>
-    <t>https://t.me/Mini_app_bazaaaaa/3
-https://t.me/Mini_app_bazaaaaa/4
-https://t.me/Mini_app_bazaaaaa/5
-https://t.me/Mini_app_bazaaaaa/6</t>
   </si>
   <si>
     <t>Imtiyozli abituriyentlar:
@@ -212,6 +202,313 @@
   </si>
   <si>
     <t>https://t.me/Mini_app_bazaaaaa/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILLIY GVARDIYA TEMURBEKLAR MAKTABI </t>
+  </si>
+  <si>
+    <t>MG TM HAL</t>
+  </si>
+  <si>
+    <t>Toshkent shahar, Yunusobod tumani</t>
+  </si>
+  <si>
+    <t>Kimlar qabul qilinadi:
+- 9-sinfni bitirgan o'quvchilar (o'g'il va qiz bolalar);
+- Bo'y: 160 sm;
+- Vazn: 60 kg;</t>
+  </si>
+  <si>
+    <t>Imtiyozli abituriyentlar:
+- Oxirgi 2 yildagi fan olimpiadasi Respublika bosqichi g’oliblari (1-o’rin);
+- Xizmat chog’ida vafot qilgan yoki nogiron bo’lib qolgan harbiy xodimlar farzandi;
+- Chin yetim yoki nosog’lom oilada yashab davlat himoyasiga muhtoj bo’lgan 9-sinf
+bitiruvchilari (Voyaga yetmagan yoshlar bilan ishlash bo’limi boshlig’i tavsiyasi bilan 5%li kvota doirasida);
+- Tegishli vazirlik vaziri tavsiyasi bilan (5%lik kvota doirasida);
+- Sport musobaqa Respublika g’oliblari (o’zi to’plagan balni 20%i qo’shib beriladi);
+O'qish davomida:
+- Bepul yotoqxona;
+- Oziq-ovqat;
+- Kiyim-kechak;
+Bitiruvchilar:
+- "BC" toifadagi haydovchilik guvohnomasi;
+- Harbiy OTMlarga 30% qo'shimcha ball;
+- OTMlarga 15% qo'shimcha ball;
+- 4% qo’shimcha kvotada
+alohida bellashuv;
+- Milliy Gvardiya institutiga
+imtihonsiz olinadi (Qizil diplom bitirsa);</t>
+  </si>
+  <si>
+    <t>Tuman mudofaa ishlari bo'limida;
+- 1-fevraldan 1-aprelgacha;</t>
+  </si>
+  <si>
+    <t>2027-02-01 09:00:00</t>
+  </si>
+  <si>
+    <t>Huquqshunoslik</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/3, https://t.me/Mini_app_bazaaaaa/4, https://t.me/Mini_app_bazaaaaa/5, https://t.me/Mini_app_bazaaaaa/6</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/14</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/15, https://t.me/Mini_app_bazaaaaa/16, https://t.me/Mini_app_bazaaaaa/17</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/18</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/19</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/20</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/21</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/22</t>
+  </si>
+  <si>
+    <t>Fizika</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/23</t>
+  </si>
+  <si>
+    <t>Aniq-2 (o'zbek)</t>
+  </si>
+  <si>
+    <t>Aniq-1 (o'zbek)</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/24</t>
+  </si>
+  <si>
+    <t>DXX TM HAL</t>
+  </si>
+  <si>
+    <t>Kimlar qabul qilinadi:
+- 9-sinfni bitirgan o'quvchilar (o'g'il bolalar(100 ta));
+- Bo'y: 165 sm;
+- Vazn: 60 kg;</t>
+  </si>
+  <si>
+    <t>Kimlar qabul qilinadi:
+- 9-sinfni bitirgan o'quvchilar (o'g'il (125 ta) va qiz (25 ta) bolalar);
+- Bo'y: 160 sm;
+- Vazn: 60 kg;</t>
+  </si>
+  <si>
+    <t>Kimlar qabul qilinadi:
+- 9-sinfni bitirgan o'quvchilar (o'g'il (185 ta) va qiz (23 ta) bolalar);</t>
+  </si>
+  <si>
+    <t>Imtiyozli abituriyentlar:
+- Oxirgi 2 yildagi fan olimpiadasi Respublika bosqichi g’oliblari (1-o’rin);
+- Xizmat chog’ida vafot qilgan yoki nogiron bo’lib qolgan harbiy xodimlar farzandi;
+- Chin yetim yoki nosog’lom oilada yashab davlat himoyasiga muhtoj bo’lgan 9-sinf
+bitiruvchilari (Voyaga yetmagan yoshlar bilan ishlash bo’limi boshlig’i tavsiyasi bilan 5%li kvota doirasida);
+- Tegishli vazirlik vaziri tavsiyasi bilan (5%lik kvota doirasida);
+- Sport musobaqa Respublika g’oliblari (o’zi to’plagan balni 20%i qo’shib beriladi);
+O'qish davomida:
+- Bepul yotoqxona;
+- Oziq-ovqat;
+- Kiyim-kechak;
+Bitiruvchilar:
+- "BC" toifadagi haydovchilik guvohnomasi;
+- Harbiy OTMlarga 30% qo'shimcha ball;
+- OTMlarga 15% qo'shimcha ball;
+- 4% qo’shimcha kvotada
+alohida bellashuv;
+- DXX akademiyasiga
+imtihonsiz olinadi (Qizil diplom bitirsa);</t>
+  </si>
+  <si>
+    <t>Tuman yoki viloyat DXX bo'limlarida;
+- 5-sentabrdan 5-oktabrgacha;</t>
+  </si>
+  <si>
+    <t>2026-09-05 09:00:00</t>
+  </si>
+  <si>
+    <t>2026-10-15 09:00:00</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/25</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/26, https://t.me/Mini_app_bazaaaaa/27, https://t.me/Mini_app_bazaaaaa/28</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/29</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/30</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/31</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/32</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/33</t>
+  </si>
+  <si>
+    <t>DAVLAT XAVFSIZLIK XIZMATI YOSH CHEGARACHILAR HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>DAVLAT XAVFSIZLIK XIZMATI TEMURBEKLAR MAKTABI HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>MILLIY GVARDIYA TEMURBEKLAR MAKTABI HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>DXX YCH HAL</t>
+  </si>
+  <si>
+    <t>Surhondaryo viloyati, Termiz shahri</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/34, https://t.me/Mini_app_bazaaaaa/35, https://t.me/Mini_app_bazaaaaa/36</t>
+  </si>
+  <si>
+    <t>ICHKI ISHLAR VAZIRLIGI TEMURBEKLAR MAKTABI HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>IIV TM HAL</t>
+  </si>
+  <si>
+    <t>Aniq (o'zbek)</t>
+  </si>
+  <si>
+    <t>Qoraqalpog'iston Respublikasi, Nukus shahri</t>
+  </si>
+  <si>
+    <t>Kimlar qabul qilinadi:
+- 9-sinfni bitirgan o'quvchilar (o'g'il bolalar(100 ta));
+- Bo'y: 160 sm;
+- Vazn: 58 kg;</t>
+  </si>
+  <si>
+    <t>Imtiyozli abituriyentlar:
+- Oxirgi 2 yildagi fan olimpiadasi Respublika bosqichi g’oliblari (1-o’rin);
+- Xizmat chog’ida vafot qilgan yoki nogiron bo’lib qolgan harbiy xodimlar farzandi;
+- Chin yetim yoki nosog’lom oilada yashab davlat himoyasiga muhtoj bo’lgan 9-sinf
+bitiruvchilari (Voyaga yetmagan yoshlar bilan ishlash bo’limi boshlig’i tavsiyasi bilan 5%li kvota doirasida);
+- Tegishli vazirlik vaziri tavsiyasi bilan (5%lik kvota doirasida);
+- Sport musobaqa Respublika g’oliblari (o’zi to’plagan balni 20%i qo’shib beriladi);
+O'qish davomida:
+- Bepul yotoqxona;
+- Oziq-ovqat;
+- Kiyim-kechak;
+Bitiruvchilar:
+- "BC" toifadagi haydovchilik guvohnomasi;
+- Harbiy OTMlarga 30% qo'shimcha ball;
+- OTMlarga 15% qo'shimcha ball;
+- 4% qo’shimcha kvotada
+alohida bellashuv;
+- Qurolli kuchlar akademiyasiga
+imtihonsiz olinadi (Qizil diplom bitirsa);</t>
+  </si>
+  <si>
+    <t>Imtiyozli abituriyentlar:
+- Oxirgi 2 yildagi fan olimpiadasi Respublika bosqichi g’oliblari (1-o’rin);
+- Xizmat chog’ida vafot qilgan yoki nogiron bo’lib qolgan harbiy xodimlar farzandi;
+- Chin yetim yoki nosog’lom oilada yashab davlat himoyasiga muhtoj bo’lgan 9-sinf
+bitiruvchilari (Voyaga yetmagan yoshlar bilan ishlash bo’limi boshlig’i tavsiyasi bilan 5%li kvota doirasida);
+- Tegishli vazirlik vaziri tavsiyasi bilan (5%lik kvota doirasida);
+- Sport musobaqa Respublika g’oliblari (o’zi to’plagan balni 20%i qo’shib beriladi);
+O'qish davomida:
+- Bepul yotoqxona;
+- Oziq-ovqat;
+- Kiyim-kechak;
+Bitiruvchilar:
+- "BC" toifadagi haydovchilik guvohnomasi;
+- Harbiy OTMlarga 30% qo'shimcha ball;
+- OTMlarga 15% qo'shimcha ball;
+- 4% qo’shimcha kvotada
+alohida bellashuv;
+- Ichki ishlar akademiyasiga
+imtihonsiz olinadi (Qizil diplom bitirsa);</t>
+  </si>
+  <si>
+    <t>Viloyat Ichki ishlar boshqarmasi orqali;
+- 1-fevraldan 1-aprelgacha;</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/37, https://t.me/Mini_app_bazaaaaa/38, https://t.me/Mini_app_bazaaaaa/39</t>
+  </si>
+  <si>
+    <t>FAVQULODDA VAZIYATLAR VAZIRLIGI TEMURBEKLAR MAKTABI HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>FVV TM HAL</t>
+  </si>
+  <si>
+    <t>Qashqadaryo viloyati, Shahrisabz tumani</t>
+  </si>
+  <si>
+    <t>Kimlar qabul qilinadi:
+- 9-sinfni bitirgan o'quvchilar (o'g'il bolalar(150 ta));
+- Bo'y: 160 sm;
+- Vazn: 58 kg;</t>
+  </si>
+  <si>
+    <t>Imtiyozli abituriyentlar:
+- Oxirgi 2 yildagi fan olimpiadasi Respublika bosqichi g’oliblari (1-o’rin);
+- Xizmat chog’ida vafot qilgan yoki nogiron bo’lib qolgan harbiy xodimlar farzandi;
+- Chin yetim yoki nosog’lom oilada yashab davlat himoyasiga muhtoj bo’lgan 9-sinf
+bitiruvchilari (Voyaga yetmagan yoshlar bilan ishlash bo’limi boshlig’i tavsiyasi bilan 5%li kvota doirasida);
+- Tegishli vazirlik vaziri tavsiyasi bilan (5%lik kvota doirasida);
+- Sport musobaqa Respublika g’oliblari (o’zi to’plagan balni 20%i qo’shib beriladi);
+O'qish davomida:
+- Bepul yotoqxona;
+- Oziq-ovqat;
+- Kiyim-kechak;
+Bitiruvchilar:
+- "BC" toifadagi haydovchilik guvohnomasi;
+- Harbiy OTMlarga 30% qo'shimcha ball;
+- OTMlarga 15% qo'shimcha ball;
+- 4% qo’shimcha kvotada
+alohida bellashuv;
+- Favqulodda vaziyatlar vazirligi akademiyasiga
+imtihonsiz olinadi (Qizil diplom bitirsa);</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/43</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/41, https://t.me/Mini_app_bazaaaaa/40, https://t.me/Mini_app_bazaaaaa/42</t>
+  </si>
+  <si>
+    <t>MUDOFAA VAZIRLIGI TEMURBEKLAR MAKTABI HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>MV TM HAL</t>
+  </si>
+  <si>
+    <t>Farg'ona viloyati, Farg'ona shahri</t>
+  </si>
+  <si>
+    <t>MUDOFAA VAZIRLIGI JALOLIDDIN MANGUBERDI HARBIY AKADEMIK LITSEYI</t>
+  </si>
+  <si>
+    <t>MV JM HAL</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/47</t>
+  </si>
+  <si>
+    <t>https://t.me/Mini_app_bazaaaaa/46, https://t.me/Mini_app_bazaaaaa/45, https://t.me/Mini_app_bazaaaaa/44</t>
+  </si>
+  <si>
+    <t>Xorazm viloyati, Urganch shahri</t>
   </si>
 </sst>
 </file>
@@ -235,12 +532,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -271,7 +574,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -286,6 +589,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -662,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>20</v>
@@ -695,10 +1001,10 @@
         <v>15</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>21</v>
@@ -710,7 +1016,7 @@
         <v>23</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>24</v>
@@ -727,7 +1033,7 @@
     </row>
     <row r="2" spans="1:32" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -736,82 +1042,82 @@
         <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="R2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="T2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="AC2" s="2">
         <v>86</v>
       </c>
       <c r="AD2" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
     </row>
     <row r="3" spans="1:32" ht="111" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -820,416 +1126,896 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="R3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="T3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="AC3" s="2">
         <v>56</v>
       </c>
       <c r="AD3" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AE3" s="2"/>
       <c r="AF3" s="2"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+    <row r="4" spans="1:32" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="3"/>
+      <c r="I4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
+      <c r="Y4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
+      <c r="AC4" s="6">
+        <v>82</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+    <row r="5" spans="1:32" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="3"/>
+      <c r="I5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
+      <c r="Y5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
+      <c r="AC5" s="6">
+        <v>59</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+    <row r="6" spans="1:32" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="3"/>
+      <c r="I6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
+      <c r="Y6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
+      <c r="AC6" s="6">
+        <v>68</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+    <row r="7" spans="1:32" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="3"/>
+      <c r="I7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
+      <c r="Y7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
+      <c r="AC7" s="6">
+        <v>86</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="AE7" s="2"/>
       <c r="AF7" s="2"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+    <row r="8" spans="1:32" ht="117" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="3"/>
+      <c r="I8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
+      <c r="Y8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
+      <c r="AC8" s="6">
+        <v>86</v>
+      </c>
+      <c r="AD8" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+    <row r="9" spans="1:32" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="3"/>
+      <c r="I9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
+      <c r="Y9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
+      <c r="AC9" s="6">
+        <v>59</v>
+      </c>
+      <c r="AD9" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="AE9" s="2"/>
       <c r="AF9" s="2"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+    <row r="10" spans="1:32" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="3"/>
+      <c r="I10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
+      <c r="Y10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
+      <c r="AC10" s="6">
+        <v>86</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+    <row r="11" spans="1:32" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="3"/>
+      <c r="I11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
+      <c r="Y11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
+      <c r="AC11" s="6">
+        <v>59</v>
+      </c>
+      <c r="AD11" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="AE11" s="2"/>
       <c r="AF11" s="2"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+    <row r="12" spans="1:32" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="3"/>
+      <c r="I12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
+      <c r="Y12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
+      <c r="AC12" s="6">
+        <v>59</v>
+      </c>
+      <c r="AD12" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="AE12" s="2"/>
       <c r="AF12" s="2"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+    <row r="13" spans="1:32" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="3"/>
+      <c r="I13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
+      <c r="Y13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
+      <c r="AC13" s="6">
+        <v>59</v>
+      </c>
+      <c r="AD13" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="AE13" s="2"/>
       <c r="AF13" s="2"/>
     </row>
@@ -3458,9 +4244,69 @@
     <hyperlink ref="Q3" r:id="rId10"/>
     <hyperlink ref="S3" r:id="rId11"/>
     <hyperlink ref="AD3" r:id="rId12"/>
+    <hyperlink ref="E4" r:id="rId13"/>
+    <hyperlink ref="M4" r:id="rId14"/>
+    <hyperlink ref="O4" r:id="rId15"/>
+    <hyperlink ref="Q4" r:id="rId16"/>
+    <hyperlink ref="S4" r:id="rId17"/>
+    <hyperlink ref="AD4" r:id="rId18"/>
+    <hyperlink ref="AD5" r:id="rId19"/>
+    <hyperlink ref="E5" r:id="rId20"/>
+    <hyperlink ref="M5" r:id="rId21"/>
+    <hyperlink ref="O5" r:id="rId22"/>
+    <hyperlink ref="Q5" r:id="rId23"/>
+    <hyperlink ref="S5" r:id="rId24"/>
+    <hyperlink ref="E6" r:id="rId25"/>
+    <hyperlink ref="M6" r:id="rId26"/>
+    <hyperlink ref="O6" r:id="rId27"/>
+    <hyperlink ref="Q6" r:id="rId28"/>
+    <hyperlink ref="S6" r:id="rId29"/>
+    <hyperlink ref="AD6" r:id="rId30"/>
+    <hyperlink ref="E7" r:id="rId31"/>
+    <hyperlink ref="M7" r:id="rId32"/>
+    <hyperlink ref="O7" r:id="rId33"/>
+    <hyperlink ref="Q7" r:id="rId34"/>
+    <hyperlink ref="S7" r:id="rId35"/>
+    <hyperlink ref="AD7" r:id="rId36"/>
+    <hyperlink ref="E8" r:id="rId37"/>
+    <hyperlink ref="M8" r:id="rId38"/>
+    <hyperlink ref="O8" r:id="rId39"/>
+    <hyperlink ref="Q8" r:id="rId40"/>
+    <hyperlink ref="S8" r:id="rId41"/>
+    <hyperlink ref="AD8" r:id="rId42"/>
+    <hyperlink ref="E9" r:id="rId43"/>
+    <hyperlink ref="M9" r:id="rId44"/>
+    <hyperlink ref="O9" r:id="rId45"/>
+    <hyperlink ref="Q9" r:id="rId46"/>
+    <hyperlink ref="S9" r:id="rId47"/>
+    <hyperlink ref="M10" r:id="rId48"/>
+    <hyperlink ref="O10" r:id="rId49"/>
+    <hyperlink ref="Q10" r:id="rId50"/>
+    <hyperlink ref="S10" r:id="rId51"/>
+    <hyperlink ref="M11" r:id="rId52"/>
+    <hyperlink ref="O11" r:id="rId53"/>
+    <hyperlink ref="Q11" r:id="rId54"/>
+    <hyperlink ref="S11" r:id="rId55"/>
+    <hyperlink ref="M12" r:id="rId56"/>
+    <hyperlink ref="O12" r:id="rId57"/>
+    <hyperlink ref="Q12" r:id="rId58"/>
+    <hyperlink ref="S12" r:id="rId59"/>
+    <hyperlink ref="AD9" r:id="rId60"/>
+    <hyperlink ref="AD10" r:id="rId61"/>
+    <hyperlink ref="E10" r:id="rId62"/>
+    <hyperlink ref="AD11" r:id="rId63"/>
+    <hyperlink ref="E11" r:id="rId64"/>
+    <hyperlink ref="AD12" r:id="rId65"/>
+    <hyperlink ref="E12" r:id="rId66"/>
+    <hyperlink ref="E13" r:id="rId67"/>
+    <hyperlink ref="M13" r:id="rId68"/>
+    <hyperlink ref="O13" r:id="rId69"/>
+    <hyperlink ref="Q13" r:id="rId70"/>
+    <hyperlink ref="S13" r:id="rId71"/>
+    <hyperlink ref="AD13" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId73"/>
 </worksheet>
 </file>
 
